--- a/step7-财险标准注释表_0824.xlsx
+++ b/step7-财险标准注释表_0824.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="84">
   <si>
     <t>模块ID</t>
   </si>
@@ -70,19 +70,16 @@
     <t>关键指标变化表</t>
   </si>
   <si>
-    <t>key_assets_equity</t>
+    <t>premium_ranking</t>
   </si>
   <si>
     <t>规模</t>
   </si>
   <si>
-    <t>总资产与净资产变化</t>
-  </si>
-  <si>
-    <t>各公司总资产与净资产规模差异显著，反映了资本实力和业务体量。</t>
-  </si>
-  <si>
-    <t>数据取自资产负债表，单位为元人民币。</t>
+    <t>保险服务收入</t>
+  </si>
+  <si>
+    <t>排名范围仅限本次研究范围内的产险单体公司。新准则口径下保险服务收入数据源自各公司年报中本公司单体口径。</t>
   </si>
   <si>
     <t>key_underwriting_profit</t>
@@ -115,28 +112,10 @@
     <t>净利润变化</t>
   </si>
   <si>
-    <t>premium_ranking</t>
+    <t>new_old_ratio</t>
   </si>
   <si>
     <t>新准则下关键年报数据</t>
-  </si>
-  <si>
-    <t>保险服务收入</t>
-  </si>
-  <si>
-    <t>保险服务收入（新准则）</t>
-  </si>
-  <si>
-    <t>新准则下保险服务收入剔除了非保险“储蓄”性质的投资成分，寿险收入显著收缩，产险受影响较小，新准则下的收入排名口径更可比。按新准则的收入排名，产险公司排名明显上升。新华人寿25年排名较24年反超阳光产险，太保产险反超平安寿险。</t>
-  </si>
-  <si>
-    <t>排名范围仅限本次研究范围内的产险单体和寿险单体公司。新准则口径下保险服务收入数据源自各公司年报中本公司单体口径。</t>
-  </si>
-  <si>
-    <t>保险业务收入（旧准则）</t>
-  </si>
-  <si>
-    <t>new_old_ratio</t>
   </si>
   <si>
     <t>新旧准则保费收入比值</t>
@@ -1039,13 +1018,13 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1599,7 +1578,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I25"/>
+  <dimension ref="A1:I23"/>
   <sheetFormatPr defaultColWidth="9.81818181818182" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="25.2727272727273" style="3" customWidth="1"/>
@@ -1658,8 +1637,8 @@
       <c r="H2" s="9"/>
       <c r="I2" s="9"/>
     </row>
-    <row r="3" s="2" customFormat="1" ht="29" spans="1:9">
-      <c r="A3" s="7" t="s">
+    <row r="3" s="2" customFormat="1" ht="72.5" spans="1:9">
+      <c r="A3" s="11" t="s">
         <v>12</v>
       </c>
       <c r="B3" s="8" t="s">
@@ -1668,451 +1647,409 @@
       <c r="C3" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="D3" s="11" t="s">
+      <c r="D3" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="E3" s="11" t="s">
+      <c r="E3" s="11"/>
+      <c r="F3" s="12"/>
+      <c r="G3" s="11" t="s">
         <v>15</v>
-      </c>
-      <c r="F3" s="9"/>
-      <c r="G3" s="11" t="s">
-        <v>16</v>
       </c>
       <c r="H3" s="9"/>
       <c r="I3" s="9"/>
     </row>
     <row r="4" s="2" customFormat="1" ht="29" spans="1:9">
-      <c r="A4" s="12" t="s">
-        <v>17</v>
+      <c r="A4" s="13" t="s">
+        <v>16</v>
       </c>
       <c r="B4" s="8" t="s">
         <v>10</v>
       </c>
       <c r="C4" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" s="10" t="s">
         <v>18</v>
-      </c>
-      <c r="D4" s="10" t="s">
-        <v>19</v>
       </c>
       <c r="E4" s="9"/>
       <c r="F4" s="9"/>
-      <c r="G4" s="13" t="s">
-        <v>20</v>
+      <c r="G4" s="14" t="s">
+        <v>19</v>
       </c>
       <c r="H4" s="9"/>
       <c r="I4" s="9"/>
     </row>
     <row r="5" s="2" customFormat="1" ht="29" spans="1:9">
-      <c r="A5" s="12" t="s">
-        <v>21</v>
+      <c r="A5" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="B5" s="8" t="s">
         <v>10</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E5" s="9"/>
       <c r="F5" s="9"/>
-      <c r="G5" s="13" t="s">
-        <v>20</v>
+      <c r="G5" s="14" t="s">
+        <v>19</v>
       </c>
       <c r="H5" s="9"/>
       <c r="I5" s="9"/>
     </row>
     <row r="6" s="2" customFormat="1" ht="29" spans="1:9">
-      <c r="A6" s="12" t="s">
-        <v>23</v>
+      <c r="A6" s="13" t="s">
+        <v>22</v>
       </c>
       <c r="B6" s="8" t="s">
         <v>10</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E6" s="9"/>
       <c r="F6" s="9"/>
-      <c r="G6" s="13" t="s">
-        <v>20</v>
+      <c r="G6" s="14" t="s">
+        <v>19</v>
       </c>
       <c r="H6" s="9"/>
       <c r="I6" s="9"/>
     </row>
     <row r="7" s="2" customFormat="1" ht="29" spans="1:9">
-      <c r="A7" s="12" t="s">
-        <v>25</v>
+      <c r="A7" s="13" t="s">
+        <v>24</v>
       </c>
       <c r="B7" s="8" t="s">
         <v>10</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E7" s="9"/>
       <c r="F7" s="9"/>
-      <c r="G7" s="13" t="s">
-        <v>20</v>
+      <c r="G7" s="14" t="s">
+        <v>19</v>
       </c>
       <c r="H7" s="9"/>
       <c r="I7" s="9"/>
     </row>
     <row r="8" ht="116" spans="1:9">
       <c r="A8" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="B8" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="B8" s="8" t="s">
+      <c r="C8" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="D8" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="C8" s="10" t="s">
+      <c r="E8" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="D8" s="10" t="s">
+      <c r="F8" s="12"/>
+      <c r="G8" s="11" t="s">
         <v>30</v>
-      </c>
-      <c r="E8" s="11" t="s">
-        <v>31</v>
-      </c>
-      <c r="F8" s="14"/>
-      <c r="G8" s="11" t="s">
-        <v>32</v>
       </c>
       <c r="H8" s="15"/>
       <c r="I8" s="15"/>
     </row>
-    <row r="9" ht="29" spans="1:9">
-      <c r="A9" s="15"/>
+    <row r="9" ht="116" spans="1:9">
+      <c r="A9" s="11" t="s">
+        <v>31</v>
+      </c>
       <c r="B9" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="D9" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="E9" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="E9" s="15"/>
-      <c r="F9" s="15"/>
-      <c r="G9" s="15"/>
+      <c r="F9" s="12"/>
+      <c r="G9" s="11" t="s">
+        <v>34</v>
+      </c>
       <c r="H9" s="15"/>
       <c r="I9" s="15"/>
     </row>
-    <row r="10" ht="116" spans="1:9">
+    <row r="10" ht="72.5" spans="1:9">
       <c r="A10" s="11" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="D10" s="15" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E10" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="F10" s="14"/>
+        <v>37</v>
+      </c>
+      <c r="F10" s="12"/>
       <c r="G10" s="11" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="H10" s="15"/>
       <c r="I10" s="15"/>
     </row>
-    <row r="11" ht="116" spans="1:9">
+    <row r="11" ht="130.5" spans="1:9">
       <c r="A11" s="11" t="s">
         <v>38</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="D11" s="15" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E11" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="F11" s="14"/>
+        <v>41</v>
+      </c>
+      <c r="F11" s="12"/>
       <c r="G11" s="11" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H11" s="15"/>
       <c r="I11" s="15"/>
     </row>
-    <row r="12" ht="72.5" spans="1:9">
+    <row r="12" ht="232" spans="1:9">
       <c r="A12" s="11" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="D12" s="15" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="F12" s="14"/>
+        <v>45</v>
+      </c>
+      <c r="F12" s="12"/>
       <c r="G12" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="H12" s="15"/>
-      <c r="I12" s="15"/>
-    </row>
-    <row r="13" ht="130.5" spans="1:9">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="13" ht="87" spans="1:9">
       <c r="A13" s="11" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="D13" s="15" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E13" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="F13" s="14"/>
+        <v>49</v>
+      </c>
+      <c r="F13" s="12"/>
       <c r="G13" s="11" t="s">
-        <v>49</v>
-      </c>
-      <c r="H13" s="15"/>
-      <c r="I13" s="15"/>
-    </row>
-    <row r="14" ht="232" spans="1:9">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="14" ht="116" spans="1:9">
       <c r="A14" s="11" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="D14" s="15" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E14" s="11" t="s">
-        <v>52</v>
-      </c>
-      <c r="F14" s="14"/>
+        <v>53</v>
+      </c>
+      <c r="F14" s="12"/>
       <c r="G14" s="11" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="15" ht="87" spans="1:9">
-      <c r="A15" s="11" t="s">
         <v>54</v>
       </c>
+    </row>
+    <row r="15" ht="43.5" spans="1:9">
+      <c r="A15" s="13" t="s">
+        <v>55</v>
+      </c>
       <c r="B15" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="D15" s="15" t="s">
-        <v>55</v>
-      </c>
-      <c r="E15" s="11" t="s">
         <v>56</v>
       </c>
-      <c r="F15" s="14"/>
-      <c r="G15" s="11" t="s">
+      <c r="D15" s="14" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="16" ht="116" spans="1:9">
-      <c r="A16" s="11" t="s">
+      <c r="E15" s="16" t="s">
         <v>58</v>
       </c>
+      <c r="F15" s="9"/>
+      <c r="G15" s="16" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="16" ht="29" spans="1:9">
+      <c r="A16" s="17"/>
       <c r="B16" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C16" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="D16" s="15" t="s">
-        <v>59</v>
-      </c>
-      <c r="E16" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="D16" s="14" t="s">
         <v>60</v>
       </c>
-      <c r="F16" s="14"/>
-      <c r="G16" s="11" t="s">
+      <c r="E16" s="18"/>
+    </row>
+    <row r="17" ht="29" spans="1:7">
+      <c r="A17" s="18"/>
+      <c r="B17" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="C17" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="D17" s="14" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="17" ht="43.5" spans="1:7">
-      <c r="A17" s="12" t="s">
+      <c r="E17" s="18"/>
+    </row>
+    <row r="18" ht="43.5" spans="1:7">
+      <c r="A18" s="19" t="s">
         <v>62</v>
       </c>
-      <c r="B17" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="C17" s="10" t="s">
+      <c r="B18" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="D17" s="13" t="s">
+      <c r="C18" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="E17" s="16" t="s">
+      <c r="D18" s="11" t="s">
         <v>65</v>
       </c>
-      <c r="F17" s="9"/>
-      <c r="G17" s="16" t="s">
+      <c r="E18" s="9"/>
+      <c r="F18" s="9"/>
+      <c r="G18" s="16" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="18" ht="29" spans="1:7">
-      <c r="A18" s="17"/>
-      <c r="B18" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="C18" s="10" t="s">
+    <row r="19" ht="43.5" spans="1:7">
+      <c r="A19" s="19" t="s">
+        <v>67</v>
+      </c>
+      <c r="B19" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="D18" s="13" t="s">
-        <v>67</v>
-      </c>
-      <c r="E18" s="18"/>
-    </row>
-    <row r="19" ht="29" spans="1:7">
-      <c r="A19" s="18"/>
-      <c r="B19" s="8" t="s">
-        <v>28</v>
-      </c>
       <c r="C19" s="10" t="s">
-        <v>63</v>
-      </c>
-      <c r="D19" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="D19" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="E19" s="18"/>
-    </row>
-    <row r="20" ht="43.5" spans="1:7">
+      <c r="E19" s="9"/>
+      <c r="F19" s="9"/>
+      <c r="G19" s="16" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="20" ht="29" spans="1:7">
       <c r="A20" s="19" t="s">
         <v>69</v>
       </c>
       <c r="B20" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="C20" s="10" t="s">
         <v>70</v>
       </c>
-      <c r="C20" s="10" t="s">
+      <c r="D20" s="11" t="s">
         <v>71</v>
       </c>
-      <c r="D20" s="11" t="s">
+    </row>
+    <row r="21" ht="29" spans="1:7">
+      <c r="A21" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="E20" s="9"/>
-      <c r="F20" s="9"/>
-      <c r="G20" s="16" t="s">
+      <c r="B21" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="C21" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="D21" s="11" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="21" ht="43.5" spans="1:7">
-      <c r="A21" s="19" t="s">
+    <row r="22" ht="87" spans="1:7">
+      <c r="A22" s="11" t="s">
         <v>74</v>
       </c>
-      <c r="B21" s="8" t="s">
-        <v>70</v>
-      </c>
-      <c r="C21" s="10" t="s">
-        <v>71</v>
-      </c>
-      <c r="D21" s="11" t="s">
+      <c r="B22" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="C22" s="10" t="s">
         <v>75</v>
       </c>
-      <c r="E21" s="9"/>
-      <c r="F21" s="9"/>
-      <c r="G21" s="16" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="22" ht="29" spans="1:7">
-      <c r="A22" s="19" t="s">
+      <c r="D22" s="11" t="s">
         <v>76</v>
       </c>
-      <c r="B22" s="8" t="s">
-        <v>70</v>
-      </c>
-      <c r="C22" s="10" t="s">
+      <c r="E22" s="11" t="s">
         <v>77</v>
       </c>
-      <c r="D22" s="11" t="s">
+      <c r="F22" s="20"/>
+      <c r="G22" s="11" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="23" ht="29" spans="1:7">
-      <c r="A23" s="7" t="s">
+    <row r="23" ht="43.5" spans="1:7">
+      <c r="A23" s="11" t="s">
         <v>79</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="C23" s="10" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="D23" s="11" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="24" ht="87" spans="1:7">
-      <c r="A24" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="B24" s="8" t="s">
-        <v>70</v>
-      </c>
-      <c r="C24" s="10" t="s">
+      <c r="E23" s="11" t="s">
         <v>82</v>
       </c>
-      <c r="D24" s="11" t="s">
+      <c r="F23" s="20"/>
+      <c r="G23" s="11" t="s">
         <v>83</v>
-      </c>
-      <c r="E24" s="11" t="s">
-        <v>84</v>
-      </c>
-      <c r="F24" s="20"/>
-      <c r="G24" s="11" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="25" ht="43.5" spans="1:7">
-      <c r="A25" s="11" t="s">
-        <v>86</v>
-      </c>
-      <c r="B25" s="8" t="s">
-        <v>70</v>
-      </c>
-      <c r="C25" s="10" t="s">
-        <v>87</v>
-      </c>
-      <c r="D25" s="11" t="s">
-        <v>88</v>
-      </c>
-      <c r="E25" s="11" t="s">
-        <v>89</v>
-      </c>
-      <c r="F25" s="20"/>
-      <c r="G25" s="11" t="s">
-        <v>90</v>
       </c>
     </row>
   </sheetData>

--- a/step7-财险标准注释表_0824.xlsx
+++ b/step7-财险标准注释表_0824.xlsx
@@ -157,7 +157,7 @@
     <t>综合成本率拆解</t>
   </si>
   <si>
-    <t>6家目标研究公司中，除阳光外，2025年综合成本率较上年均有改善；人保、平安、太平因规模效应，综合费用率呈现优势。2025年综合成本率横向对比下，众安产险综合成本率最低，平安产险较上年综合成本率改善最明显。新准则下2025年综合费用率普遍同比下降，综合赔付率普遍同比上升。</t>
+    <t>太平产险年报中未详细披露综合费用率和综合赔付率</t>
   </si>
   <si>
     <t>综合成本率 = （保险服务费用 + 承保财务损益 + 再保净成本 + 提取保费准备金）/ 保险服务收入。</t>
@@ -1811,7 +1811,7 @@
       <c r="H10" s="15"/>
       <c r="I10" s="15"/>
     </row>
-    <row r="11" ht="130.5" spans="1:9">
+    <row r="11" ht="58" spans="1:9">
       <c r="A11" s="11" t="s">
         <v>38</v>
       </c>

--- a/step7-财险标准注释表_0824.xlsx
+++ b/step7-财险标准注释表_0824.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="87">
   <si>
     <t>模块ID</t>
   </si>
@@ -76,55 +76,64 @@
     <t>规模</t>
   </si>
   <si>
+    <t>保险服务收入（新准则）</t>
+  </si>
+  <si>
+    <t>排名范围仅限本次研究范围内的产险单体公司。新准则口径下保险服务收入数据源自各公司年报中本公司单体口径。</t>
+  </si>
+  <si>
+    <t>premium_old</t>
+  </si>
+  <si>
+    <t>保险业务收入（旧准则）</t>
+  </si>
+  <si>
+    <t>旧准则口径下保费收入数据源自偿付能力报告“保险业务收入”。</t>
+  </si>
+  <si>
+    <t>key_underwriting_profit</t>
+  </si>
+  <si>
+    <t>效益</t>
+  </si>
+  <si>
+    <t>保险服务业绩</t>
+  </si>
+  <si>
+    <t>数据取自利润表，单位为元人民币。</t>
+  </si>
+  <si>
+    <t>key_investment_profit</t>
+  </si>
+  <si>
+    <t>投资服务业绩</t>
+  </si>
+  <si>
+    <t>key_profit_composition</t>
+  </si>
+  <si>
+    <t>净利润的贡献</t>
+  </si>
+  <si>
+    <t>key_net_profit</t>
+  </si>
+  <si>
+    <t>净利润变化</t>
+  </si>
+  <si>
+    <t>new_old_ratio</t>
+  </si>
+  <si>
+    <t>新准则下关键年报数据</t>
+  </si>
+  <si>
     <t>保险服务收入</t>
   </si>
   <si>
-    <t>排名范围仅限本次研究范围内的产险单体公司。新准则口径下保险服务收入数据源自各公司年报中本公司单体口径。</t>
-  </si>
-  <si>
-    <t>key_underwriting_profit</t>
-  </si>
-  <si>
-    <t>效益</t>
-  </si>
-  <si>
-    <t>保险服务业绩</t>
-  </si>
-  <si>
-    <t>数据取自利润表，单位为元人民币。</t>
-  </si>
-  <si>
-    <t>key_investment_profit</t>
-  </si>
-  <si>
-    <t>投资服务业绩</t>
-  </si>
-  <si>
-    <t>key_profit_composition</t>
-  </si>
-  <si>
-    <t>净利润的贡献</t>
-  </si>
-  <si>
-    <t>key_net_profit</t>
-  </si>
-  <si>
-    <t>净利润变化</t>
-  </si>
-  <si>
-    <t>new_old_ratio</t>
-  </si>
-  <si>
-    <t>新准则下关键年报数据</t>
-  </si>
-  <si>
     <t>新旧准则保费收入比值</t>
   </si>
   <si>
     <t>准则实施三年，新旧准则下的保费收入差异范围持续收窄，2025年为92%–101%，2024年为90%–102%。25年仅阳光产险保险服务收入（新准则口径）高于保险业务收入（旧准则口径）；受投资成分扣除影响，人保产险的该比例连续三年最低。</t>
-  </si>
-  <si>
-    <t>旧准则口径下保费收入数据源自偿付能力报告“保险业务收入”。</t>
   </si>
   <si>
     <t>investment_component</t>
@@ -981,7 +990,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1020,6 +1029,9 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -1578,7 +1590,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I23"/>
+  <dimension ref="A1:I24"/>
   <sheetFormatPr defaultColWidth="9.81818181818182" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="25.2727272727273" style="3" customWidth="1"/>
@@ -1658,7 +1670,7 @@
       <c r="H3" s="9"/>
       <c r="I3" s="9"/>
     </row>
-    <row r="4" s="2" customFormat="1" ht="29" spans="1:9">
+    <row r="4" s="2" customFormat="1" ht="43.5" spans="1:9">
       <c r="A4" s="13" t="s">
         <v>16</v>
       </c>
@@ -1666,116 +1678,114 @@
         <v>10</v>
       </c>
       <c r="C4" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4" s="10" t="s">
         <v>17</v>
-      </c>
-      <c r="D4" s="10" t="s">
-        <v>18</v>
       </c>
       <c r="E4" s="9"/>
       <c r="F4" s="9"/>
-      <c r="G4" s="14" t="s">
-        <v>19</v>
+      <c r="G4" s="11" t="s">
+        <v>18</v>
       </c>
       <c r="H4" s="9"/>
       <c r="I4" s="9"/>
     </row>
     <row r="5" s="2" customFormat="1" ht="29" spans="1:9">
-      <c r="A5" s="13" t="s">
-        <v>20</v>
+      <c r="A5" s="14" t="s">
+        <v>19</v>
       </c>
       <c r="B5" s="8" t="s">
         <v>10</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D5" s="10" t="s">
         <v>21</v>
       </c>
       <c r="E5" s="9"/>
       <c r="F5" s="9"/>
-      <c r="G5" s="14" t="s">
-        <v>19</v>
+      <c r="G5" s="15" t="s">
+        <v>22</v>
       </c>
       <c r="H5" s="9"/>
       <c r="I5" s="9"/>
     </row>
     <row r="6" s="2" customFormat="1" ht="29" spans="1:9">
-      <c r="A6" s="13" t="s">
-        <v>22</v>
+      <c r="A6" s="14" t="s">
+        <v>23</v>
       </c>
       <c r="B6" s="8" t="s">
         <v>10</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E6" s="9"/>
       <c r="F6" s="9"/>
-      <c r="G6" s="14" t="s">
-        <v>19</v>
+      <c r="G6" s="15" t="s">
+        <v>22</v>
       </c>
       <c r="H6" s="9"/>
       <c r="I6" s="9"/>
     </row>
     <row r="7" s="2" customFormat="1" ht="29" spans="1:9">
-      <c r="A7" s="13" t="s">
-        <v>24</v>
+      <c r="A7" s="14" t="s">
+        <v>25</v>
       </c>
       <c r="B7" s="8" t="s">
         <v>10</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E7" s="9"/>
       <c r="F7" s="9"/>
-      <c r="G7" s="14" t="s">
-        <v>19</v>
+      <c r="G7" s="15" t="s">
+        <v>22</v>
       </c>
       <c r="H7" s="9"/>
       <c r="I7" s="9"/>
     </row>
-    <row r="8" ht="116" spans="1:9">
-      <c r="A8" s="11" t="s">
-        <v>26</v>
+    <row r="8" s="2" customFormat="1" ht="29" spans="1:9">
+      <c r="A8" s="14" t="s">
+        <v>27</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="D8" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="D8" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="E8" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="F8" s="12"/>
-      <c r="G8" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="H8" s="15"/>
-      <c r="I8" s="15"/>
+      <c r="E8" s="9"/>
+      <c r="F8" s="9"/>
+      <c r="G8" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="H8" s="9"/>
+      <c r="I8" s="9"/>
     </row>
     <row r="9" ht="116" spans="1:9">
       <c r="A9" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="C9" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="B9" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="C9" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="D9" s="15" t="s">
+      <c r="D9" s="16" t="s">
         <v>32</v>
       </c>
       <c r="E9" s="11" t="s">
@@ -1783,273 +1793,296 @@
       </c>
       <c r="F9" s="12"/>
       <c r="G9" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="H9" s="16"/>
+      <c r="I9" s="16"/>
+    </row>
+    <row r="10" ht="116" spans="1:9">
+      <c r="A10" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="H9" s="15"/>
-      <c r="I9" s="15"/>
-    </row>
-    <row r="10" ht="72.5" spans="1:9">
-      <c r="A10" s="11" t="s">
+      <c r="B10" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="C10" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="D10" s="16" t="s">
         <v>35</v>
       </c>
-      <c r="B10" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="C10" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="D10" s="15" t="s">
+      <c r="E10" s="11" t="s">
         <v>36</v>
-      </c>
-      <c r="E10" s="11" t="s">
-        <v>37</v>
       </c>
       <c r="F10" s="12"/>
       <c r="G10" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="H10" s="15"/>
-      <c r="I10" s="15"/>
-    </row>
-    <row r="11" ht="58" spans="1:9">
+        <v>37</v>
+      </c>
+      <c r="H10" s="16"/>
+      <c r="I10" s="16"/>
+    </row>
+    <row r="11" ht="72.5" spans="1:9">
       <c r="A11" s="11" t="s">
         <v>38</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C11" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="D11" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="D11" s="15" t="s">
+      <c r="E11" s="11" t="s">
         <v>40</v>
-      </c>
-      <c r="E11" s="11" t="s">
-        <v>41</v>
       </c>
       <c r="F11" s="12"/>
       <c r="G11" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="H11" s="16"/>
+      <c r="I11" s="16"/>
+    </row>
+    <row r="12" ht="58" spans="1:9">
+      <c r="A12" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="B12" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="C12" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="H11" s="15"/>
-      <c r="I11" s="15"/>
-    </row>
-    <row r="12" ht="232" spans="1:9">
-      <c r="A12" s="11" t="s">
+      <c r="D12" s="16" t="s">
         <v>43</v>
       </c>
-      <c r="B12" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="C12" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="D12" s="15" t="s">
+      <c r="E12" s="11" t="s">
         <v>44</v>
-      </c>
-      <c r="E12" s="11" t="s">
-        <v>45</v>
       </c>
       <c r="F12" s="12"/>
       <c r="G12" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="H12" s="16"/>
+      <c r="I12" s="16"/>
+    </row>
+    <row r="13" ht="232" spans="1:9">
+      <c r="A13" s="11" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="13" ht="87" spans="1:9">
-      <c r="A13" s="11" t="s">
+      <c r="B13" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="C13" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="D13" s="16" t="s">
         <v>47</v>
       </c>
-      <c r="B13" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="C13" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="D13" s="15" t="s">
+      <c r="E13" s="11" t="s">
         <v>48</v>
-      </c>
-      <c r="E13" s="11" t="s">
-        <v>49</v>
       </c>
       <c r="F13" s="12"/>
       <c r="G13" s="11" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="14" ht="87" spans="1:9">
+      <c r="A14" s="11" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="14" ht="116" spans="1:9">
-      <c r="A14" s="11" t="s">
+      <c r="B14" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="C14" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="D14" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="B14" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="C14" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="D14" s="15" t="s">
+      <c r="E14" s="11" t="s">
         <v>52</v>
-      </c>
-      <c r="E14" s="11" t="s">
-        <v>53</v>
       </c>
       <c r="F14" s="12"/>
       <c r="G14" s="11" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="15" ht="116" spans="1:9">
+      <c r="A15" s="11" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="15" ht="43.5" spans="1:9">
-      <c r="A15" s="13" t="s">
+      <c r="B15" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="C15" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="D15" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="B15" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="C15" s="10" t="s">
+      <c r="E15" s="11" t="s">
         <v>56</v>
       </c>
-      <c r="D15" s="14" t="s">
+      <c r="F15" s="12"/>
+      <c r="G15" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="E15" s="16" t="s">
+    </row>
+    <row r="16" ht="43.5" spans="1:9">
+      <c r="A16" s="14" t="s">
         <v>58</v>
       </c>
-      <c r="F15" s="9"/>
-      <c r="G15" s="16" t="s">
+      <c r="B16" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="C16" s="10" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="16" ht="29" spans="1:9">
-      <c r="A16" s="17"/>
-      <c r="B16" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="C16" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="D16" s="14" t="s">
+      <c r="D16" s="15" t="s">
         <v>60</v>
       </c>
-      <c r="E16" s="18"/>
+      <c r="E16" s="17" t="s">
+        <v>61</v>
+      </c>
+      <c r="F16" s="9"/>
+      <c r="G16" s="17" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="17" ht="29" spans="1:7">
       <c r="A17" s="18"/>
       <c r="B17" s="8" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C17" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="D17" s="14" t="s">
-        <v>61</v>
-      </c>
-      <c r="E17" s="18"/>
-    </row>
-    <row r="18" ht="43.5" spans="1:7">
-      <c r="A18" s="19" t="s">
-        <v>62</v>
-      </c>
+        <v>59</v>
+      </c>
+      <c r="D17" s="15" t="s">
+        <v>63</v>
+      </c>
+      <c r="E17" s="19"/>
+    </row>
+    <row r="18" ht="29" spans="1:7">
+      <c r="A18" s="19"/>
       <c r="B18" s="8" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="C18" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="D18" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="D18" s="11" t="s">
+      <c r="E18" s="19"/>
+    </row>
+    <row r="19" ht="43.5" spans="1:7">
+      <c r="A19" s="20" t="s">
         <v>65</v>
       </c>
-      <c r="E18" s="9"/>
-      <c r="F18" s="9"/>
-      <c r="G18" s="16" t="s">
+      <c r="B19" s="8" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="19" ht="43.5" spans="1:7">
-      <c r="A19" s="19" t="s">
+      <c r="C19" s="10" t="s">
         <v>67</v>
-      </c>
-      <c r="B19" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="C19" s="10" t="s">
-        <v>64</v>
       </c>
       <c r="D19" s="11" t="s">
         <v>68</v>
       </c>
       <c r="E19" s="9"/>
       <c r="F19" s="9"/>
-      <c r="G19" s="16" t="s">
+      <c r="G19" s="17" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="20" ht="43.5" spans="1:7">
+      <c r="A20" s="20" t="s">
+        <v>70</v>
+      </c>
+      <c r="B20" s="8" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="20" ht="29" spans="1:7">
-      <c r="A20" s="19" t="s">
-        <v>69</v>
-      </c>
-      <c r="B20" s="8" t="s">
-        <v>63</v>
-      </c>
       <c r="C20" s="10" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="D20" s="11" t="s">
         <v>71</v>
       </c>
+      <c r="E20" s="9"/>
+      <c r="F20" s="9"/>
+      <c r="G20" s="17" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="21" ht="29" spans="1:7">
-      <c r="A21" s="7" t="s">
+      <c r="A21" s="20" t="s">
         <v>72</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="C21" s="10" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="D21" s="11" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="22" ht="29" spans="1:7">
+      <c r="A22" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="B22" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="C22" s="10" t="s">
         <v>73</v>
-      </c>
-    </row>
-    <row r="22" ht="87" spans="1:7">
-      <c r="A22" s="11" t="s">
-        <v>74</v>
-      </c>
-      <c r="B22" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="C22" s="10" t="s">
-        <v>75</v>
       </c>
       <c r="D22" s="11" t="s">
         <v>76</v>
       </c>
-      <c r="E22" s="11" t="s">
+    </row>
+    <row r="23" ht="87" spans="1:7">
+      <c r="A23" s="11" t="s">
         <v>77</v>
       </c>
-      <c r="F22" s="20"/>
-      <c r="G22" s="11" t="s">
+      <c r="B23" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="C23" s="10" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="23" ht="43.5" spans="1:7">
-      <c r="A23" s="11" t="s">
+      <c r="D23" s="11" t="s">
         <v>79</v>
       </c>
-      <c r="B23" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="C23" s="10" t="s">
+      <c r="E23" s="11" t="s">
         <v>80</v>
       </c>
-      <c r="D23" s="11" t="s">
+      <c r="F23" s="21"/>
+      <c r="G23" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="E23" s="11" t="s">
+    </row>
+    <row r="24" ht="43.5" spans="1:7">
+      <c r="A24" s="11" t="s">
         <v>82</v>
       </c>
-      <c r="F23" s="20"/>
-      <c r="G23" s="11" t="s">
+      <c r="B24" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="C24" s="10" t="s">
         <v>83</v>
+      </c>
+      <c r="D24" s="11" t="s">
+        <v>84</v>
+      </c>
+      <c r="E24" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="F24" s="21"/>
+      <c r="G24" s="11" t="s">
+        <v>86</v>
       </c>
     </row>
   </sheetData>

--- a/step7-财险标准注释表_0824.xlsx
+++ b/step7-财险标准注释表_0824.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="89">
   <si>
     <t>模块ID</t>
   </si>
@@ -223,7 +223,13 @@
     <t>数据基于保险合同负债及资产表计算，单位为百分比。</t>
   </si>
   <si>
+    <t>discount_rate</t>
+  </si>
+  <si>
     <t>折现率披露</t>
+  </si>
+  <si>
+    <t>risk_margin</t>
   </si>
   <si>
     <t>非金融风险调整披露</t>
@@ -305,7 +311,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="27">
+  <fonts count="26">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -346,12 +352,6 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="7"/>
-      <color rgb="FF0F1115"/>
-      <name val="Consolas"/>
       <charset val="134"/>
     </font>
     <font>
@@ -860,137 +860,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1043,9 +1043,6 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -1952,7 +1949,9 @@
       </c>
     </row>
     <row r="17" ht="29" spans="1:7">
-      <c r="A17" s="18"/>
+      <c r="A17" s="13" t="s">
+        <v>63</v>
+      </c>
       <c r="B17" s="8" t="s">
         <v>30</v>
       </c>
@@ -1960,12 +1959,14 @@
         <v>59</v>
       </c>
       <c r="D17" s="15" t="s">
-        <v>63</v>
-      </c>
-      <c r="E17" s="19"/>
+        <v>64</v>
+      </c>
+      <c r="E17" s="18"/>
     </row>
     <row r="18" ht="29" spans="1:7">
-      <c r="A18" s="19"/>
+      <c r="A18" s="13" t="s">
+        <v>65</v>
+      </c>
       <c r="B18" s="8" t="s">
         <v>30</v>
       </c>
@@ -1973,116 +1974,116 @@
         <v>59</v>
       </c>
       <c r="D18" s="15" t="s">
-        <v>64</v>
-      </c>
-      <c r="E18" s="19"/>
+        <v>66</v>
+      </c>
+      <c r="E18" s="18"/>
     </row>
     <row r="19" ht="43.5" spans="1:7">
-      <c r="A19" s="20" t="s">
-        <v>65</v>
+      <c r="A19" s="19" t="s">
+        <v>67</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C19" s="10" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D19" s="11" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E19" s="9"/>
       <c r="F19" s="9"/>
       <c r="G19" s="17" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="20" ht="43.5" spans="1:7">
+      <c r="A20" s="19" t="s">
+        <v>72</v>
+      </c>
+      <c r="B20" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="C20" s="10" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="20" ht="43.5" spans="1:7">
-      <c r="A20" s="20" t="s">
-        <v>70</v>
-      </c>
-      <c r="B20" s="8" t="s">
-        <v>66</v>
-      </c>
-      <c r="C20" s="10" t="s">
-        <v>67</v>
-      </c>
       <c r="D20" s="11" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="E20" s="9"/>
       <c r="F20" s="9"/>
       <c r="G20" s="17" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
     <row r="21" ht="29" spans="1:7">
-      <c r="A21" s="20" t="s">
-        <v>72</v>
+      <c r="A21" s="19" t="s">
+        <v>74</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C21" s="10" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D21" s="11" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="22" ht="29" spans="1:7">
       <c r="A22" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="B22" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="C22" s="10" t="s">
         <v>75</v>
       </c>
-      <c r="B22" s="8" t="s">
-        <v>66</v>
-      </c>
-      <c r="C22" s="10" t="s">
-        <v>73</v>
-      </c>
       <c r="D22" s="11" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
     </row>
     <row r="23" ht="87" spans="1:7">
       <c r="A23" s="11" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C23" s="10" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D23" s="11" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E23" s="11" t="s">
-        <v>80</v>
-      </c>
-      <c r="F23" s="21"/>
+        <v>82</v>
+      </c>
+      <c r="F23" s="20"/>
       <c r="G23" s="11" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="24" ht="43.5" spans="1:7">
       <c r="A24" s="11" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C24" s="10" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D24" s="11" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E24" s="11" t="s">
-        <v>85</v>
-      </c>
-      <c r="F24" s="21"/>
+        <v>87</v>
+      </c>
+      <c r="F24" s="20"/>
       <c r="G24" s="11" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
   </sheetData>
